--- a/CELC.xlsx
+++ b/CELC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8551A1-6091-4317-817C-F176698B7B8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A04E0C5-444C-4E9C-BA5E-D018D487603B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47720" yWindow="2830" windowWidth="28800" windowHeight="15370" activeTab="1" xr2:uid="{0B25212F-A640-401E-AFFE-298C447892E3}"/>
+    <workbookView xWindow="19360" yWindow="3050" windowWidth="19170" windowHeight="13220" activeTab="1" xr2:uid="{0B25212F-A640-401E-AFFE-298C447892E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t>Price</t>
   </si>
@@ -57,9 +57,6 @@
     <t>EV</t>
   </si>
   <si>
-    <t>Q125</t>
-  </si>
-  <si>
     <t>gedatolisib</t>
   </si>
   <si>
@@ -103,6 +100,18 @@
   </si>
   <si>
     <t>no-mutation HFS HR=0.85</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>PIC</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>4/8/2021: paid Pfizer $5m to license gedatolisib</t>
   </si>
 </sst>
 </file>
@@ -162,7 +171,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -170,22 +179,117 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -521,67 +625,162 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D56D7E5-E57F-45FF-96CC-715915D2C8E0}">
-  <dimension ref="B2:M7"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B2:M11"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.08984375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.36328125" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="16"/>
+      <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="1">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" t="s">
+      <c r="L2" s="5">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="10"/>
+      <c r="K3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L3" s="2">
-        <v>37.866357999999998</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="K4" t="s">
+      <c r="L3" s="6">
+        <v>48.336675</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10"/>
+      <c r="K4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="6">
         <f>+L2*L3</f>
-        <v>1741.8524679999998</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="K5" t="s">
+        <v>6912.1445249999997</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B5" s="8"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="10"/>
+      <c r="K5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L5" s="2">
-        <f>16.478+189.213</f>
-        <v>205.691</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="K6" t="s">
+      <c r="L5" s="6">
+        <f>165.703+275.794</f>
+        <v>441.49699999999996</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B6" s="8"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10"/>
+      <c r="K6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="2">
-        <v>98.527000000000001</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.35">
-      <c r="K7" t="s">
+      <c r="L6" s="6">
+        <f>195.324+126.527</f>
+        <v>321.851</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="8"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="10"/>
+      <c r="K7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="6">
         <f>+L4-L5+L6</f>
-        <v>1634.6884679999998</v>
+        <v>6792.4985249999991</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="13"/>
+      <c r="K9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L9" s="6">
+        <v>549.404</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="K10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" s="6">
+        <v>448.89699999999999</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -594,75 +793,75 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.7265625" style="4"/>
+    <col min="1" max="1" width="4.6328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+      <c r="C4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C6" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C6" s="7" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C7" s="4" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C8" s="4" t="s">
+    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C9" s="6" t="s">
+    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C11" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C12" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C11" s="7" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="1" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="13" x14ac:dyDescent="0.3">
-      <c r="C12" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C13" s="4" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
